--- a/#Mali_anonymized.xlsx
+++ b/#Mali_anonymized.xlsx
@@ -525,7 +525,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -568,7 +568,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -610,7 +610,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -696,7 +696,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -739,7 +739,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -3334,7 +3334,7 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -3374,7 +3374,7 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -3415,7 +3415,7 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -3457,7 +3457,7 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -3501,7 +3501,7 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -3551,7 +3551,7 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -9847,7 +9847,7 @@
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -9889,7 +9889,7 @@
       </c>
       <c r="J270" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -9931,7 +9931,7 @@
       </c>
       <c r="J271" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -9973,7 +9973,7 @@
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -10015,7 +10015,7 @@
       </c>
       <c r="J273" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -16728,7 +16728,7 @@
       </c>
       <c r="J471" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -16772,7 +16772,7 @@
       </c>
       <c r="J472" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -16817,7 +16817,7 @@
       </c>
       <c r="J473" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -22302,7 +22302,7 @@
       </c>
       <c r="J636" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -23559,7 +23559,7 @@
       </c>
       <c r="J673" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -23601,7 +23601,7 @@
       </c>
       <c r="J674" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -24945,7 +24945,7 @@
       </c>
       <c r="J714" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -24990,7 +24990,7 @@
       </c>
       <c r="J715" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -27646,7 +27646,7 @@
       </c>
       <c r="J795" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -29028,7 +29028,7 @@
       </c>
       <c r="J837" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
